--- a/data-raw/versteeg.maize.xlsx
+++ b/data-raw/versteeg.maize.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\drop\rpack\agridat\data-raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEA51A2A-BE98-4F68-AFCF-5345A2B15BFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{540E02B8-50D3-4D4C-96C4-01347098CBC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{46C9002E-909F-42D1-816A-1556D837AC48}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{46C9002E-909F-42D1-816A-1556D837AC48}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -183,9 +183,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -523,2122 +522,2119 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98A31747-186D-47D6-BD2B-8FA5BE270324}">
   <dimension ref="A1:F151"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="16384" width="8.7265625" style="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="2">
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="1">
         <v>2.375</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="2">
+      <c r="B3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="1">
         <v>1.8140000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="2">
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="1">
         <v>3.0649999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" s="2">
+      <c r="B5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="1">
         <v>2.085</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6" s="2">
+      <c r="B6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="1">
         <v>1.4930000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D7" s="2">
+      <c r="B7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" s="1">
         <v>1.1279999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D8" s="2">
+      <c r="B8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" s="1">
         <v>2.3340000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="1" t="s">
+      <c r="A9" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D9" s="2">
+      <c r="B9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" s="1">
         <v>1.4590000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="1" t="s">
+      <c r="A10" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D10" s="2">
+      <c r="B10" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10" s="1">
         <v>1.99</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="1" t="s">
+      <c r="A11" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D11" s="2">
+      <c r="B11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11" s="1">
         <v>1.32</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="1" t="s">
+      <c r="A12" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D12" s="2">
+      <c r="B12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D12" s="1">
         <v>1.7769999999999999</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" s="1" t="s">
+      <c r="A13" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D13" s="2">
+      <c r="B13" t="s">
+        <v>3</v>
+      </c>
+      <c r="C13" t="s">
+        <v>5</v>
+      </c>
+      <c r="D13" s="1">
         <v>1.0840000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" s="1" t="s">
+      <c r="A14" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D14" s="2">
+      <c r="B14" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14" t="s">
+        <v>5</v>
+      </c>
+      <c r="D14" s="1">
         <v>1.387</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" s="1" t="s">
+      <c r="A15" t="s">
         <v>22</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D15" s="2">
+      <c r="B15" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" t="s">
+        <v>5</v>
+      </c>
+      <c r="D15" s="1">
         <v>1.2450000000000001</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" s="1" t="s">
+      <c r="A16" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D16" s="2">
+      <c r="B16" t="s">
+        <v>3</v>
+      </c>
+      <c r="C16" t="s">
+        <v>5</v>
+      </c>
+      <c r="D16" s="1">
         <v>2.601</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" s="1" t="s">
+      <c r="A17" t="s">
         <v>24</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D17" s="2">
+      <c r="B17" t="s">
+        <v>3</v>
+      </c>
+      <c r="C17" t="s">
+        <v>5</v>
+      </c>
+      <c r="D17" s="1">
         <v>1.925</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" s="1" t="s">
+      <c r="A18" t="s">
         <v>25</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D18" s="2">
+      <c r="B18" t="s">
+        <v>3</v>
+      </c>
+      <c r="C18" t="s">
+        <v>5</v>
+      </c>
+      <c r="D18" s="1">
         <v>0.19400000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" s="1" t="s">
+      <c r="A19" t="s">
         <v>26</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D19" s="2">
+      <c r="B19" t="s">
+        <v>3</v>
+      </c>
+      <c r="C19" t="s">
+        <v>5</v>
+      </c>
+      <c r="D19" s="1">
         <v>2.3180000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" s="1" t="s">
+      <c r="A20" t="s">
         <v>27</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D20" s="2">
+      <c r="B20" t="s">
+        <v>3</v>
+      </c>
+      <c r="C20" t="s">
+        <v>5</v>
+      </c>
+      <c r="D20" s="1">
         <v>0.64600000000000002</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" s="1" t="s">
+      <c r="A21" t="s">
         <v>28</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D21" s="2">
+      <c r="B21" t="s">
+        <v>3</v>
+      </c>
+      <c r="C21" t="s">
+        <v>5</v>
+      </c>
+      <c r="D21" s="1">
         <v>1.62</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" s="1" t="s">
+      <c r="A22" t="s">
         <v>29</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D22" s="2">
+      <c r="B22" t="s">
+        <v>3</v>
+      </c>
+      <c r="C22" t="s">
+        <v>5</v>
+      </c>
+      <c r="D22" s="1">
         <v>1.462</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" s="1" t="s">
+      <c r="A23" t="s">
         <v>30</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D23" s="2">
+      <c r="B23" t="s">
+        <v>3</v>
+      </c>
+      <c r="C23" t="s">
+        <v>5</v>
+      </c>
+      <c r="D23" s="1">
         <v>1.3169999999999999</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" s="1" t="s">
+      <c r="A24" t="s">
         <v>31</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D24" s="2">
+      <c r="B24" t="s">
+        <v>3</v>
+      </c>
+      <c r="C24" t="s">
+        <v>5</v>
+      </c>
+      <c r="D24" s="1">
         <v>0.73</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" s="1" t="s">
+      <c r="A25" t="s">
         <v>32</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D25" s="2">
+      <c r="B25" t="s">
+        <v>3</v>
+      </c>
+      <c r="C25" t="s">
+        <v>5</v>
+      </c>
+      <c r="D25" s="1">
         <v>1.617</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A26" s="1" t="s">
+      <c r="A26" t="s">
         <v>33</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D26" s="2">
+      <c r="B26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C26" t="s">
+        <v>5</v>
+      </c>
+      <c r="D26" s="1">
         <v>1.458</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" s="1" t="s">
+      <c r="A27" t="s">
         <v>9</v>
       </c>
-      <c r="B27" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D27" s="2">
+      <c r="B27" t="s">
+        <v>4</v>
+      </c>
+      <c r="C27" t="s">
+        <v>5</v>
+      </c>
+      <c r="D27" s="1">
         <v>2.363</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A28" s="1" t="s">
+      <c r="A28" t="s">
         <v>10</v>
       </c>
-      <c r="B28" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D28" s="2">
+      <c r="B28" t="s">
+        <v>4</v>
+      </c>
+      <c r="C28" t="s">
+        <v>5</v>
+      </c>
+      <c r="D28" s="1">
         <v>2.4350000000000001</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A29" s="1" t="s">
+      <c r="A29" t="s">
         <v>11</v>
       </c>
-      <c r="B29" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D29" s="2">
+      <c r="B29" t="s">
+        <v>4</v>
+      </c>
+      <c r="C29" t="s">
+        <v>5</v>
+      </c>
+      <c r="D29" s="1">
         <v>2.11</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A30" s="1" t="s">
+      <c r="A30" t="s">
         <v>12</v>
       </c>
-      <c r="B30" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D30" s="2">
+      <c r="B30" t="s">
+        <v>4</v>
+      </c>
+      <c r="C30" t="s">
+        <v>5</v>
+      </c>
+      <c r="D30" s="1">
         <v>1.958</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A31" s="1" t="s">
+      <c r="A31" t="s">
         <v>13</v>
       </c>
-      <c r="B31" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D31" s="2">
+      <c r="B31" t="s">
+        <v>4</v>
+      </c>
+      <c r="C31" t="s">
+        <v>5</v>
+      </c>
+      <c r="D31" s="1">
         <v>1.4790000000000001</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A32" s="1" t="s">
+      <c r="A32" t="s">
         <v>14</v>
       </c>
-      <c r="B32" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D32" s="2">
+      <c r="B32" t="s">
+        <v>4</v>
+      </c>
+      <c r="C32" t="s">
+        <v>5</v>
+      </c>
+      <c r="D32" s="1">
         <v>1.524</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A33" s="1" t="s">
+      <c r="A33" t="s">
         <v>15</v>
       </c>
-      <c r="B33" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D33" s="2">
+      <c r="B33" t="s">
+        <v>4</v>
+      </c>
+      <c r="C33" t="s">
+        <v>5</v>
+      </c>
+      <c r="D33" s="1">
         <v>1.6579999999999999</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A34" s="1" t="s">
+      <c r="A34" t="s">
         <v>16</v>
       </c>
-      <c r="B34" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D34" s="2">
+      <c r="B34" t="s">
+        <v>4</v>
+      </c>
+      <c r="C34" t="s">
+        <v>5</v>
+      </c>
+      <c r="D34" s="1">
         <v>0.83</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A35" s="1" t="s">
+      <c r="A35" t="s">
         <v>17</v>
       </c>
-      <c r="B35" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D35" s="2">
+      <c r="B35" t="s">
+        <v>4</v>
+      </c>
+      <c r="C35" t="s">
+        <v>5</v>
+      </c>
+      <c r="D35" s="1">
         <v>2.2829999999999999</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A36" s="1" t="s">
+      <c r="A36" t="s">
         <v>18</v>
       </c>
-      <c r="B36" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D36" s="2">
+      <c r="B36" t="s">
+        <v>4</v>
+      </c>
+      <c r="C36" t="s">
+        <v>5</v>
+      </c>
+      <c r="D36" s="1">
         <v>0.99099999999999999</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A37" s="1" t="s">
+      <c r="A37" t="s">
         <v>19</v>
       </c>
-      <c r="B37" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D37" s="2">
+      <c r="B37" t="s">
+        <v>4</v>
+      </c>
+      <c r="C37" t="s">
+        <v>5</v>
+      </c>
+      <c r="D37" s="1">
         <v>1.7010000000000001</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A38" s="1" t="s">
+      <c r="A38" t="s">
         <v>20</v>
       </c>
-      <c r="B38" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D38" s="2">
+      <c r="B38" t="s">
+        <v>4</v>
+      </c>
+      <c r="C38" t="s">
+        <v>5</v>
+      </c>
+      <c r="D38" s="1">
         <v>1.1970000000000001</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A39" s="1" t="s">
+      <c r="A39" t="s">
         <v>21</v>
       </c>
-      <c r="B39" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D39" s="2">
+      <c r="B39" t="s">
+        <v>4</v>
+      </c>
+      <c r="C39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D39" s="1">
         <v>1.1419999999999999</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A40" s="1" t="s">
+      <c r="A40" t="s">
         <v>22</v>
       </c>
-      <c r="B40" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D40" s="2">
+      <c r="B40" t="s">
+        <v>4</v>
+      </c>
+      <c r="C40" t="s">
+        <v>5</v>
+      </c>
+      <c r="D40" s="1">
         <v>1.2290000000000001</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A41" s="1" t="s">
+      <c r="A41" t="s">
         <v>23</v>
       </c>
-      <c r="B41" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D41" s="2">
+      <c r="B41" t="s">
+        <v>4</v>
+      </c>
+      <c r="C41" t="s">
+        <v>5</v>
+      </c>
+      <c r="D41" s="1">
         <v>2.9489999999999998</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A42" s="1" t="s">
+      <c r="A42" t="s">
         <v>24</v>
       </c>
-      <c r="B42" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D42" s="2">
+      <c r="B42" t="s">
+        <v>4</v>
+      </c>
+      <c r="C42" t="s">
+        <v>5</v>
+      </c>
+      <c r="D42" s="1">
         <v>1.7589999999999999</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A43" s="1" t="s">
+      <c r="A43" t="s">
         <v>25</v>
       </c>
-      <c r="B43" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D43" s="2">
+      <c r="B43" t="s">
+        <v>4</v>
+      </c>
+      <c r="C43" t="s">
+        <v>5</v>
+      </c>
+      <c r="D43" s="1">
         <v>0.192</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A44" s="1" t="s">
+      <c r="A44" t="s">
         <v>26</v>
       </c>
-      <c r="B44" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D44" s="2">
+      <c r="B44" t="s">
+        <v>4</v>
+      </c>
+      <c r="C44" t="s">
+        <v>5</v>
+      </c>
+      <c r="D44" s="1">
         <v>1.9239999999999999</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A45" s="1" t="s">
+      <c r="A45" t="s">
         <v>27</v>
       </c>
-      <c r="B45" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D45" s="2">
+      <c r="B45" t="s">
+        <v>4</v>
+      </c>
+      <c r="C45" t="s">
+        <v>5</v>
+      </c>
+      <c r="D45" s="1">
         <v>0.91800000000000004</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A46" s="1" t="s">
+      <c r="A46" t="s">
         <v>28</v>
       </c>
-      <c r="B46" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D46" s="2">
+      <c r="B46" t="s">
+        <v>4</v>
+      </c>
+      <c r="C46" t="s">
+        <v>5</v>
+      </c>
+      <c r="D46" s="1">
         <v>0.99399999999999999</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A47" s="1" t="s">
+      <c r="A47" t="s">
         <v>29</v>
       </c>
-      <c r="B47" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D47" s="2">
+      <c r="B47" t="s">
+        <v>4</v>
+      </c>
+      <c r="C47" t="s">
+        <v>5</v>
+      </c>
+      <c r="D47" s="1">
         <v>1.5109999999999999</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A48" s="1" t="s">
+      <c r="A48" t="s">
         <v>30</v>
       </c>
-      <c r="B48" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D48" s="2">
+      <c r="B48" t="s">
+        <v>4</v>
+      </c>
+      <c r="C48" t="s">
+        <v>5</v>
+      </c>
+      <c r="D48" s="1">
         <v>0.88700000000000001</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A49" s="1" t="s">
+      <c r="A49" t="s">
         <v>31</v>
       </c>
-      <c r="B49" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D49" s="2">
+      <c r="B49" t="s">
+        <v>4</v>
+      </c>
+      <c r="C49" t="s">
+        <v>5</v>
+      </c>
+      <c r="D49" s="1">
         <v>0.48</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A50" s="1" t="s">
+      <c r="A50" t="s">
         <v>32</v>
       </c>
-      <c r="B50" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D50" s="2">
+      <c r="B50" t="s">
+        <v>4</v>
+      </c>
+      <c r="C50" t="s">
+        <v>5</v>
+      </c>
+      <c r="D50" s="1">
         <v>1.306</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A51" s="1" t="s">
+      <c r="A51" t="s">
         <v>33</v>
       </c>
-      <c r="B51" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D51" s="2">
+      <c r="B51" t="s">
+        <v>4</v>
+      </c>
+      <c r="C51" t="s">
+        <v>5</v>
+      </c>
+      <c r="D51" s="1">
         <v>0.47599999999999998</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A52" s="1" t="s">
+      <c r="A52" t="s">
         <v>9</v>
       </c>
-      <c r="B52" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D52" s="2">
+      <c r="B52" t="s">
+        <v>3</v>
+      </c>
+      <c r="C52" t="s">
+        <v>6</v>
+      </c>
+      <c r="D52" s="1">
         <v>2.0779999999999998</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A53" s="1" t="s">
+      <c r="A53" t="s">
         <v>10</v>
       </c>
-      <c r="B53" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D53" s="2">
+      <c r="B53" t="s">
+        <v>3</v>
+      </c>
+      <c r="C53" t="s">
+        <v>6</v>
+      </c>
+      <c r="D53" s="1">
         <v>1.6970000000000001</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A54" s="1" t="s">
+      <c r="A54" t="s">
         <v>11</v>
       </c>
-      <c r="B54" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D54" s="2">
+      <c r="B54" t="s">
+        <v>3</v>
+      </c>
+      <c r="C54" t="s">
+        <v>6</v>
+      </c>
+      <c r="D54" s="1">
         <v>3.081</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A55" s="1" t="s">
+      <c r="A55" t="s">
         <v>12</v>
       </c>
-      <c r="B55" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D55" s="2">
+      <c r="B55" t="s">
+        <v>3</v>
+      </c>
+      <c r="C55" t="s">
+        <v>6</v>
+      </c>
+      <c r="D55" s="1">
         <v>1.2050000000000001</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A56" s="1" t="s">
+      <c r="A56" t="s">
         <v>13</v>
       </c>
-      <c r="B56" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D56" s="2">
+      <c r="B56" t="s">
+        <v>3</v>
+      </c>
+      <c r="C56" t="s">
+        <v>6</v>
+      </c>
+      <c r="D56" s="1">
         <v>2.2050000000000001</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A57" s="1" t="s">
+      <c r="A57" t="s">
         <v>14</v>
       </c>
-      <c r="B57" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D57" s="2">
+      <c r="B57" t="s">
+        <v>3</v>
+      </c>
+      <c r="C57" t="s">
+        <v>6</v>
+      </c>
+      <c r="D57" s="1">
         <v>1.24</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A58" s="1" t="s">
+      <c r="A58" t="s">
         <v>15</v>
       </c>
-      <c r="B58" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D58" s="2">
+      <c r="B58" t="s">
+        <v>3</v>
+      </c>
+      <c r="C58" t="s">
+        <v>6</v>
+      </c>
+      <c r="D58" s="1">
         <v>2.573</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A59" s="1" t="s">
+      <c r="A59" t="s">
         <v>16</v>
       </c>
-      <c r="B59" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D59" s="2">
+      <c r="B59" t="s">
+        <v>3</v>
+      </c>
+      <c r="C59" t="s">
+        <v>6</v>
+      </c>
+      <c r="D59" s="1">
         <v>1.8420000000000001</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A60" s="1" t="s">
+      <c r="A60" t="s">
         <v>17</v>
       </c>
-      <c r="B60" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D60" s="2">
+      <c r="B60" t="s">
+        <v>3</v>
+      </c>
+      <c r="C60" t="s">
+        <v>6</v>
+      </c>
+      <c r="D60" s="1">
         <v>2.4079999999999999</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A61" s="1" t="s">
+      <c r="A61" t="s">
         <v>18</v>
       </c>
-      <c r="B61" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D61" s="2">
+      <c r="B61" t="s">
+        <v>3</v>
+      </c>
+      <c r="C61" t="s">
+        <v>6</v>
+      </c>
+      <c r="D61" s="1">
         <v>1.6859999999999999</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A62" s="1" t="s">
+      <c r="A62" t="s">
         <v>19</v>
       </c>
-      <c r="B62" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D62" s="2">
+      <c r="B62" t="s">
+        <v>3</v>
+      </c>
+      <c r="C62" t="s">
+        <v>6</v>
+      </c>
+      <c r="D62" s="1">
         <v>1.6479999999999999</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A63" s="1" t="s">
+      <c r="A63" t="s">
         <v>20</v>
       </c>
-      <c r="B63" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D63" s="2">
+      <c r="B63" t="s">
+        <v>3</v>
+      </c>
+      <c r="C63" t="s">
+        <v>6</v>
+      </c>
+      <c r="D63" s="1">
         <v>1.5449999999999999</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A64" s="1" t="s">
+      <c r="A64" t="s">
         <v>21</v>
       </c>
-      <c r="B64" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D64" s="2">
+      <c r="B64" t="s">
+        <v>3</v>
+      </c>
+      <c r="C64" t="s">
+        <v>6</v>
+      </c>
+      <c r="D64" s="1">
         <v>2.0960000000000001</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A65" s="1" t="s">
+      <c r="A65" t="s">
         <v>22</v>
       </c>
-      <c r="B65" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D65" s="2">
+      <c r="B65" t="s">
+        <v>3</v>
+      </c>
+      <c r="C65" t="s">
+        <v>6</v>
+      </c>
+      <c r="D65" s="1">
         <v>1.675</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A66" s="1" t="s">
+      <c r="A66" t="s">
         <v>23</v>
       </c>
-      <c r="B66" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D66" s="2">
+      <c r="B66" t="s">
+        <v>3</v>
+      </c>
+      <c r="C66" t="s">
+        <v>6</v>
+      </c>
+      <c r="D66" s="1">
         <v>3.4740000000000002</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A67" s="1" t="s">
+      <c r="A67" t="s">
         <v>24</v>
       </c>
-      <c r="B67" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D67" s="2">
+      <c r="B67" t="s">
+        <v>3</v>
+      </c>
+      <c r="C67" t="s">
+        <v>6</v>
+      </c>
+      <c r="D67" s="1">
         <v>3.081</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A68" s="1" t="s">
+      <c r="A68" t="s">
         <v>25</v>
       </c>
-      <c r="B68" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D68" s="2">
+      <c r="B68" t="s">
+        <v>3</v>
+      </c>
+      <c r="C68" t="s">
+        <v>6</v>
+      </c>
+      <c r="D68" s="1">
         <v>4.8000000000000001E-2</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A69" s="1" t="s">
+      <c r="A69" t="s">
         <v>26</v>
       </c>
-      <c r="B69" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D69" s="2">
+      <c r="B69" t="s">
+        <v>3</v>
+      </c>
+      <c r="C69" t="s">
+        <v>6</v>
+      </c>
+      <c r="D69" s="1">
         <v>2.6280000000000001</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A70" s="1" t="s">
+      <c r="A70" t="s">
         <v>27</v>
       </c>
-      <c r="B70" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D70" s="2">
+      <c r="B70" t="s">
+        <v>3</v>
+      </c>
+      <c r="C70" t="s">
+        <v>6</v>
+      </c>
+      <c r="D70" s="1">
         <v>1.909</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A71" s="1" t="s">
+      <c r="A71" t="s">
         <v>28</v>
       </c>
-      <c r="B71" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D71" s="2">
+      <c r="B71" t="s">
+        <v>3</v>
+      </c>
+      <c r="C71" t="s">
+        <v>6</v>
+      </c>
+      <c r="D71" s="1">
         <v>1.429</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A72" s="1" t="s">
+      <c r="A72" t="s">
         <v>29</v>
       </c>
-      <c r="B72" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D72" s="2">
+      <c r="B72" t="s">
+        <v>3</v>
+      </c>
+      <c r="C72" t="s">
+        <v>6</v>
+      </c>
+      <c r="D72" s="1">
         <v>2.2160000000000002</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A73" s="1" t="s">
+      <c r="A73" t="s">
         <v>30</v>
       </c>
-      <c r="B73" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D73" s="2">
+      <c r="B73" t="s">
+        <v>3</v>
+      </c>
+      <c r="C73" t="s">
+        <v>6</v>
+      </c>
+      <c r="D73" s="1">
         <v>1.921</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A74" s="1" t="s">
+      <c r="A74" t="s">
         <v>31</v>
       </c>
-      <c r="B74" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D74" s="2">
+      <c r="B74" t="s">
+        <v>3</v>
+      </c>
+      <c r="C74" t="s">
+        <v>6</v>
+      </c>
+      <c r="D74" s="1">
         <v>0.79</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A75" s="1" t="s">
+      <c r="A75" t="s">
         <v>32</v>
       </c>
-      <c r="B75" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D75" s="2">
+      <c r="B75" t="s">
+        <v>3</v>
+      </c>
+      <c r="C75" t="s">
+        <v>6</v>
+      </c>
+      <c r="D75" s="1">
         <v>1.49</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A76" s="1" t="s">
+      <c r="A76" t="s">
         <v>33</v>
       </c>
-      <c r="B76" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D76" s="2">
+      <c r="B76" t="s">
+        <v>3</v>
+      </c>
+      <c r="C76" t="s">
+        <v>6</v>
+      </c>
+      <c r="D76" s="1">
         <v>1.0309999999999999</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A77" s="1" t="s">
+      <c r="A77" t="s">
         <v>9</v>
       </c>
-      <c r="B77" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D77" s="2">
+      <c r="B77" t="s">
+        <v>4</v>
+      </c>
+      <c r="C77" t="s">
+        <v>6</v>
+      </c>
+      <c r="D77" s="1">
         <v>2.444</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A78" s="1" t="s">
+      <c r="A78" t="s">
         <v>10</v>
       </c>
-      <c r="B78" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D78" s="2">
+      <c r="B78" t="s">
+        <v>4</v>
+      </c>
+      <c r="C78" t="s">
+        <v>6</v>
+      </c>
+      <c r="D78" s="1">
         <v>2.6840000000000002</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A79" s="1" t="s">
+      <c r="A79" t="s">
         <v>11</v>
       </c>
-      <c r="B79" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D79" s="2">
+      <c r="B79" t="s">
+        <v>4</v>
+      </c>
+      <c r="C79" t="s">
+        <v>6</v>
+      </c>
+      <c r="D79" s="1">
         <v>3.76</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A80" s="1" t="s">
+      <c r="A80" t="s">
         <v>12</v>
       </c>
-      <c r="B80" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D80" s="2">
+      <c r="B80" t="s">
+        <v>4</v>
+      </c>
+      <c r="C80" t="s">
+        <v>6</v>
+      </c>
+      <c r="D80" s="1">
         <v>1.194</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A81" s="1" t="s">
+      <c r="A81" t="s">
         <v>13</v>
       </c>
-      <c r="B81" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C81" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D81" s="2">
+      <c r="B81" t="s">
+        <v>4</v>
+      </c>
+      <c r="C81" t="s">
+        <v>6</v>
+      </c>
+      <c r="D81" s="1">
         <v>2.2730000000000001</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A82" s="1" t="s">
+      <c r="A82" t="s">
         <v>14</v>
       </c>
-      <c r="B82" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D82" s="2">
+      <c r="B82" t="s">
+        <v>4</v>
+      </c>
+      <c r="C82" t="s">
+        <v>6</v>
+      </c>
+      <c r="D82" s="1">
         <v>1.651</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A83" s="1" t="s">
+      <c r="A83" t="s">
         <v>15</v>
       </c>
-      <c r="B83" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D83" s="2">
+      <c r="B83" t="s">
+        <v>4</v>
+      </c>
+      <c r="C83" t="s">
+        <v>6</v>
+      </c>
+      <c r="D83" s="1">
         <v>3.129</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A84" s="1" t="s">
+      <c r="A84" t="s">
         <v>16</v>
       </c>
-      <c r="B84" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D84" s="2">
+      <c r="B84" t="s">
+        <v>4</v>
+      </c>
+      <c r="C84" t="s">
+        <v>6</v>
+      </c>
+      <c r="D84" s="1">
         <v>0.57799999999999996</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A85" s="1" t="s">
+      <c r="A85" t="s">
         <v>17</v>
       </c>
-      <c r="B85" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D85" s="2">
+      <c r="B85" t="s">
+        <v>4</v>
+      </c>
+      <c r="C85" t="s">
+        <v>6</v>
+      </c>
+      <c r="D85" s="1">
         <v>1.647</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A86" s="1" t="s">
+      <c r="A86" t="s">
         <v>18</v>
       </c>
-      <c r="B86" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D86" s="2">
+      <c r="B86" t="s">
+        <v>4</v>
+      </c>
+      <c r="C86" t="s">
+        <v>6</v>
+      </c>
+      <c r="D86" s="1">
         <v>0.71199999999999997</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A87" s="1" t="s">
+      <c r="A87" t="s">
         <v>19</v>
       </c>
-      <c r="B87" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C87" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D87" s="2">
+      <c r="B87" t="s">
+        <v>4</v>
+      </c>
+      <c r="C87" t="s">
+        <v>6</v>
+      </c>
+      <c r="D87" s="1">
         <v>2.2250000000000001</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A88" s="1" t="s">
+      <c r="A88" t="s">
         <v>20</v>
       </c>
-      <c r="B88" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C88" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D88" s="2">
+      <c r="B88" t="s">
+        <v>4</v>
+      </c>
+      <c r="C88" t="s">
+        <v>6</v>
+      </c>
+      <c r="D88" s="1">
         <v>1.796</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A89" s="1" t="s">
+      <c r="A89" t="s">
         <v>21</v>
       </c>
-      <c r="B89" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D89" s="2">
+      <c r="B89" t="s">
+        <v>4</v>
+      </c>
+      <c r="C89" t="s">
+        <v>6</v>
+      </c>
+      <c r="D89" s="1">
         <v>2.802</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A90" s="1" t="s">
+      <c r="A90" t="s">
         <v>22</v>
       </c>
-      <c r="B90" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C90" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D90" s="2">
+      <c r="B90" t="s">
+        <v>4</v>
+      </c>
+      <c r="C90" t="s">
+        <v>6</v>
+      </c>
+      <c r="D90" s="1">
         <v>1.9419999999999999</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A91" s="1" t="s">
+      <c r="A91" t="s">
         <v>23</v>
       </c>
-      <c r="B91" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C91" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D91" s="2">
+      <c r="B91" t="s">
+        <v>4</v>
+      </c>
+      <c r="C91" t="s">
+        <v>6</v>
+      </c>
+      <c r="D91" s="1">
         <v>3.0230000000000001</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A92" s="1" t="s">
+      <c r="A92" t="s">
         <v>24</v>
       </c>
-      <c r="B92" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C92" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D92" s="2">
+      <c r="B92" t="s">
+        <v>4</v>
+      </c>
+      <c r="C92" t="s">
+        <v>6</v>
+      </c>
+      <c r="D92" s="1">
         <v>3.5510000000000002</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A93" s="1" t="s">
+      <c r="A93" t="s">
         <v>25</v>
       </c>
-      <c r="B93" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D93" s="2">
+      <c r="B93" t="s">
+        <v>4</v>
+      </c>
+      <c r="C93" t="s">
+        <v>6</v>
+      </c>
+      <c r="D93" s="1">
         <v>0.159</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A94" s="1" t="s">
+      <c r="A94" t="s">
         <v>26</v>
       </c>
-      <c r="B94" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C94" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D94" s="2">
+      <c r="B94" t="s">
+        <v>4</v>
+      </c>
+      <c r="C94" t="s">
+        <v>6</v>
+      </c>
+      <c r="D94" s="1">
         <v>1.99</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A95" s="1" t="s">
+      <c r="A95" t="s">
         <v>27</v>
       </c>
-      <c r="B95" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C95" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D95" s="2">
+      <c r="B95" t="s">
+        <v>4</v>
+      </c>
+      <c r="C95" t="s">
+        <v>6</v>
+      </c>
+      <c r="D95" s="1">
         <v>2.4500000000000002</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A96" s="1" t="s">
+      <c r="A96" t="s">
         <v>28</v>
       </c>
-      <c r="B96" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C96" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D96" s="2">
+      <c r="B96" t="s">
+        <v>4</v>
+      </c>
+      <c r="C96" t="s">
+        <v>6</v>
+      </c>
+      <c r="D96" s="1">
         <v>0.66100000000000003</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A97" s="1" t="s">
+      <c r="A97" t="s">
         <v>29</v>
       </c>
-      <c r="B97" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C97" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D97" s="2">
+      <c r="B97" t="s">
+        <v>4</v>
+      </c>
+      <c r="C97" t="s">
+        <v>6</v>
+      </c>
+      <c r="D97" s="1">
         <v>1.901</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A98" s="1" t="s">
+      <c r="A98" t="s">
         <v>30</v>
       </c>
-      <c r="B98" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D98" s="2">
+      <c r="B98" t="s">
+        <v>4</v>
+      </c>
+      <c r="C98" t="s">
+        <v>6</v>
+      </c>
+      <c r="D98" s="1">
         <v>2.282</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A99" s="1" t="s">
+      <c r="A99" t="s">
         <v>31</v>
       </c>
-      <c r="B99" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C99" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D99" s="2">
+      <c r="B99" t="s">
+        <v>4</v>
+      </c>
+      <c r="C99" t="s">
+        <v>6</v>
+      </c>
+      <c r="D99" s="1">
         <v>0.72199999999999998</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A100" s="1" t="s">
+      <c r="A100" t="s">
         <v>32</v>
       </c>
-      <c r="B100" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C100" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D100" s="2">
+      <c r="B100" t="s">
+        <v>4</v>
+      </c>
+      <c r="C100" t="s">
+        <v>6</v>
+      </c>
+      <c r="D100" s="1">
         <v>1.4970000000000001</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A101" s="1" t="s">
+      <c r="A101" t="s">
         <v>33</v>
       </c>
-      <c r="B101" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C101" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D101" s="2">
+      <c r="B101" t="s">
+        <v>4</v>
+      </c>
+      <c r="C101" t="s">
+        <v>6</v>
+      </c>
+      <c r="D101" s="1">
         <v>1.327</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A102" s="1" t="s">
+      <c r="A102" t="s">
         <v>9</v>
       </c>
-      <c r="B102" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C102" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D102" s="2">
+      <c r="B102" t="s">
+        <v>3</v>
+      </c>
+      <c r="C102" t="s">
+        <v>7</v>
+      </c>
+      <c r="D102" s="1">
         <v>3.544</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A103" s="1" t="s">
+      <c r="A103" t="s">
         <v>10</v>
       </c>
-      <c r="B103" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C103" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D103" s="2">
+      <c r="B103" t="s">
+        <v>3</v>
+      </c>
+      <c r="C103" t="s">
+        <v>7</v>
+      </c>
+      <c r="D103" s="1">
         <v>2.984</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A104" s="1" t="s">
+      <c r="A104" t="s">
         <v>11</v>
       </c>
-      <c r="B104" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C104" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D104" s="2">
+      <c r="B104" t="s">
+        <v>3</v>
+      </c>
+      <c r="C104" t="s">
+        <v>7</v>
+      </c>
+      <c r="D104" s="1">
         <v>4.13</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A105" s="1" t="s">
+      <c r="A105" t="s">
         <v>12</v>
       </c>
-      <c r="B105" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C105" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D105" s="2">
+      <c r="B105" t="s">
+        <v>3</v>
+      </c>
+      <c r="C105" t="s">
+        <v>7</v>
+      </c>
+      <c r="D105" s="1">
         <v>2.0619999999999998</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A106" s="1" t="s">
+      <c r="A106" t="s">
         <v>13</v>
       </c>
-      <c r="B106" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C106" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D106" s="2">
+      <c r="B106" t="s">
+        <v>3</v>
+      </c>
+      <c r="C106" t="s">
+        <v>7</v>
+      </c>
+      <c r="D106" s="1">
         <v>2.044</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A107" s="1" t="s">
+      <c r="A107" t="s">
         <v>14</v>
       </c>
-      <c r="B107" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C107" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D107" s="2">
+      <c r="B107" t="s">
+        <v>3</v>
+      </c>
+      <c r="C107" t="s">
+        <v>7</v>
+      </c>
+      <c r="D107" s="1">
         <v>1.268</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A108" s="1" t="s">
+      <c r="A108" t="s">
         <v>15</v>
       </c>
-      <c r="B108" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C108" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D108" s="2">
+      <c r="B108" t="s">
+        <v>3</v>
+      </c>
+      <c r="C108" t="s">
+        <v>7</v>
+      </c>
+      <c r="D108" s="1">
         <v>4.1550000000000002</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A109" s="1" t="s">
+      <c r="A109" t="s">
         <v>16</v>
       </c>
-      <c r="B109" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C109" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D109" s="2">
+      <c r="B109" t="s">
+        <v>3</v>
+      </c>
+      <c r="C109" t="s">
+        <v>7</v>
+      </c>
+      <c r="D109" s="1">
         <v>1.798</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A110" s="1" t="s">
+      <c r="A110" t="s">
         <v>17</v>
       </c>
-      <c r="B110" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C110" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D110" s="2">
+      <c r="B110" t="s">
+        <v>3</v>
+      </c>
+      <c r="C110" t="s">
+        <v>7</v>
+      </c>
+      <c r="D110" s="1">
         <v>2.57</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A111" s="1" t="s">
+      <c r="A111" t="s">
         <v>18</v>
       </c>
-      <c r="B111" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C111" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D111" s="2">
+      <c r="B111" t="s">
+        <v>3</v>
+      </c>
+      <c r="C111" t="s">
+        <v>7</v>
+      </c>
+      <c r="D111" s="1">
         <v>2.3239999999999998</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A112" s="1" t="s">
+      <c r="A112" t="s">
         <v>19</v>
       </c>
-      <c r="B112" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C112" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D112" s="2">
+      <c r="B112" t="s">
+        <v>3</v>
+      </c>
+      <c r="C112" t="s">
+        <v>7</v>
+      </c>
+      <c r="D112" s="1">
         <v>2.0539999999999998</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A113" s="1" t="s">
+      <c r="A113" t="s">
         <v>20</v>
       </c>
-      <c r="B113" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C113" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D113" s="2">
+      <c r="B113" t="s">
+        <v>3</v>
+      </c>
+      <c r="C113" t="s">
+        <v>7</v>
+      </c>
+      <c r="D113" s="1">
         <v>1.583</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A114" s="1" t="s">
+      <c r="A114" t="s">
         <v>21</v>
       </c>
-      <c r="B114" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C114" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D114" s="2">
+      <c r="B114" t="s">
+        <v>3</v>
+      </c>
+      <c r="C114" t="s">
+        <v>7</v>
+      </c>
+      <c r="D114" s="1">
         <v>1.454</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A115" s="1" t="s">
+      <c r="A115" t="s">
         <v>22</v>
       </c>
-      <c r="B115" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C115" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D115" s="2">
+      <c r="B115" t="s">
+        <v>3</v>
+      </c>
+      <c r="C115" t="s">
+        <v>7</v>
+      </c>
+      <c r="D115" s="1">
         <v>1.99</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A116" s="1" t="s">
+      <c r="A116" t="s">
         <v>23</v>
       </c>
-      <c r="B116" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C116" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D116" s="2">
+      <c r="B116" t="s">
+        <v>3</v>
+      </c>
+      <c r="C116" t="s">
+        <v>7</v>
+      </c>
+      <c r="D116" s="1">
         <v>4.5640000000000001</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A117" s="1" t="s">
+      <c r="A117" t="s">
         <v>24</v>
       </c>
-      <c r="B117" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C117" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D117" s="2">
+      <c r="B117" t="s">
+        <v>3</v>
+      </c>
+      <c r="C117" t="s">
+        <v>7</v>
+      </c>
+      <c r="D117" s="1">
         <v>2.8</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A118" s="1" t="s">
+      <c r="A118" t="s">
         <v>25</v>
       </c>
-      <c r="B118" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C118" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D118" s="2">
+      <c r="B118" t="s">
+        <v>3</v>
+      </c>
+      <c r="C118" t="s">
+        <v>7</v>
+      </c>
+      <c r="D118" s="1">
         <v>0.78500000000000003</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A119" s="1" t="s">
+      <c r="A119" t="s">
         <v>26</v>
       </c>
-      <c r="B119" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C119" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D119" s="2">
+      <c r="B119" t="s">
+        <v>3</v>
+      </c>
+      <c r="C119" t="s">
+        <v>7</v>
+      </c>
+      <c r="D119" s="1">
         <v>2.97</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A120" s="1" t="s">
+      <c r="A120" t="s">
         <v>27</v>
       </c>
-      <c r="B120" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C120" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D120" s="2">
+      <c r="B120" t="s">
+        <v>3</v>
+      </c>
+      <c r="C120" t="s">
+        <v>7</v>
+      </c>
+      <c r="D120" s="1">
         <v>0.81</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A121" s="1" t="s">
+      <c r="A121" t="s">
         <v>28</v>
       </c>
-      <c r="B121" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C121" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D121" s="2">
+      <c r="B121" t="s">
+        <v>3</v>
+      </c>
+      <c r="C121" t="s">
+        <v>7</v>
+      </c>
+      <c r="D121" s="1">
         <v>1.6319999999999999</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A122" s="1" t="s">
+      <c r="A122" t="s">
         <v>29</v>
       </c>
-      <c r="B122" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C122" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D122" s="2">
+      <c r="B122" t="s">
+        <v>3</v>
+      </c>
+      <c r="C122" t="s">
+        <v>7</v>
+      </c>
+      <c r="D122" s="1">
         <v>2.794</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A123" s="1" t="s">
+      <c r="A123" t="s">
         <v>30</v>
       </c>
-      <c r="B123" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C123" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D123" s="2">
+      <c r="B123" t="s">
+        <v>3</v>
+      </c>
+      <c r="C123" t="s">
+        <v>7</v>
+      </c>
+      <c r="D123" s="1">
         <v>0.48599999999999999</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A124" s="1" t="s">
+      <c r="A124" t="s">
         <v>31</v>
       </c>
-      <c r="B124" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C124" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D124" s="2">
+      <c r="B124" t="s">
+        <v>3</v>
+      </c>
+      <c r="C124" t="s">
+        <v>7</v>
+      </c>
+      <c r="D124" s="1">
         <v>0.58299999999999996</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A125" s="1" t="s">
+      <c r="A125" t="s">
         <v>32</v>
       </c>
-      <c r="B125" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C125" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D125" s="2">
+      <c r="B125" t="s">
+        <v>3</v>
+      </c>
+      <c r="C125" t="s">
+        <v>7</v>
+      </c>
+      <c r="D125" s="1">
         <v>2.226</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A126" s="1" t="s">
+      <c r="A126" t="s">
         <v>33</v>
       </c>
-      <c r="B126" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C126" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D126" s="2">
+      <c r="B126" t="s">
+        <v>3</v>
+      </c>
+      <c r="C126" t="s">
+        <v>7</v>
+      </c>
+      <c r="D126" s="1">
         <v>0.879</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A127" s="1" t="s">
+      <c r="A127" t="s">
         <v>9</v>
       </c>
-      <c r="B127" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C127" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D127" s="2">
+      <c r="B127" t="s">
+        <v>4</v>
+      </c>
+      <c r="C127" t="s">
+        <v>7</v>
+      </c>
+      <c r="D127" s="1">
         <v>1.5660000000000001</v>
       </c>
-      <c r="F127" s="2"/>
+      <c r="F127" s="1"/>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A128" s="1" t="s">
+      <c r="A128" t="s">
         <v>10</v>
       </c>
-      <c r="B128" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C128" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D128" s="2">
+      <c r="B128" t="s">
+        <v>4</v>
+      </c>
+      <c r="C128" t="s">
+        <v>7</v>
+      </c>
+      <c r="D128" s="1">
         <v>3.758</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A129" s="1" t="s">
+      <c r="A129" t="s">
         <v>11</v>
       </c>
-      <c r="B129" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C129" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D129" s="2">
+      <c r="B129" t="s">
+        <v>4</v>
+      </c>
+      <c r="C129" t="s">
+        <v>7</v>
+      </c>
+      <c r="D129" s="1">
         <v>3.52</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A130" s="1" t="s">
+      <c r="A130" t="s">
         <v>12</v>
       </c>
-      <c r="B130" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C130" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D130" s="2">
+      <c r="B130" t="s">
+        <v>4</v>
+      </c>
+      <c r="C130" t="s">
+        <v>7</v>
+      </c>
+      <c r="D130" s="1">
         <v>2.35</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A131" s="1" t="s">
+      <c r="A131" t="s">
         <v>13</v>
       </c>
-      <c r="B131" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C131" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D131" s="2">
+      <c r="B131" t="s">
+        <v>4</v>
+      </c>
+      <c r="C131" t="s">
+        <v>7</v>
+      </c>
+      <c r="D131" s="1">
         <v>2.2909999999999999</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A132" s="1" t="s">
+      <c r="A132" t="s">
         <v>14</v>
       </c>
-      <c r="B132" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C132" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D132" s="2">
+      <c r="B132" t="s">
+        <v>4</v>
+      </c>
+      <c r="C132" t="s">
+        <v>7</v>
+      </c>
+      <c r="D132" s="1">
         <v>1.8169999999999999</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A133" s="1" t="s">
+      <c r="A133" t="s">
         <v>15</v>
       </c>
-      <c r="B133" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C133" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D133" s="2">
+      <c r="B133" t="s">
+        <v>4</v>
+      </c>
+      <c r="C133" t="s">
+        <v>7</v>
+      </c>
+      <c r="D133" s="1">
         <v>3.8450000000000002</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A134" s="1" t="s">
+      <c r="A134" t="s">
         <v>16</v>
       </c>
-      <c r="B134" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C134" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D134" s="2">
+      <c r="B134" t="s">
+        <v>4</v>
+      </c>
+      <c r="C134" t="s">
+        <v>7</v>
+      </c>
+      <c r="D134" s="1">
         <v>0.97799999999999998</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A135" s="1" t="s">
+      <c r="A135" t="s">
         <v>17</v>
       </c>
-      <c r="B135" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C135" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D135" s="2">
+      <c r="B135" t="s">
+        <v>4</v>
+      </c>
+      <c r="C135" t="s">
+        <v>7</v>
+      </c>
+      <c r="D135" s="1">
         <v>2.746</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A136" s="1" t="s">
+      <c r="A136" t="s">
         <v>18</v>
       </c>
-      <c r="B136" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C136" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D136" s="2">
+      <c r="B136" t="s">
+        <v>4</v>
+      </c>
+      <c r="C136" t="s">
+        <v>7</v>
+      </c>
+      <c r="D136" s="1">
         <v>1.998</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A137" s="1" t="s">
+      <c r="A137" t="s">
         <v>19</v>
       </c>
-      <c r="B137" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C137" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D137" s="2">
+      <c r="B137" t="s">
+        <v>4</v>
+      </c>
+      <c r="C137" t="s">
+        <v>7</v>
+      </c>
+      <c r="D137" s="1">
         <v>2.0939999999999999</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A138" s="1" t="s">
+      <c r="A138" t="s">
         <v>20</v>
       </c>
-      <c r="B138" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C138" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D138" s="2">
+      <c r="B138" t="s">
+        <v>4</v>
+      </c>
+      <c r="C138" t="s">
+        <v>7</v>
+      </c>
+      <c r="D138" s="1">
         <v>1.5580000000000001</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A139" s="1" t="s">
+      <c r="A139" t="s">
         <v>21</v>
       </c>
-      <c r="B139" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C139" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D139" s="2">
+      <c r="B139" t="s">
+        <v>4</v>
+      </c>
+      <c r="C139" t="s">
+        <v>7</v>
+      </c>
+      <c r="D139" s="1">
         <v>3.0659999999999998</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A140" s="1" t="s">
+      <c r="A140" t="s">
         <v>22</v>
       </c>
-      <c r="B140" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C140" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D140" s="2">
+      <c r="B140" t="s">
+        <v>4</v>
+      </c>
+      <c r="C140" t="s">
+        <v>7</v>
+      </c>
+      <c r="D140" s="1">
         <v>2.0449999999999999</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A141" s="1" t="s">
+      <c r="A141" t="s">
         <v>23</v>
       </c>
-      <c r="B141" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C141" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D141" s="2">
+      <c r="B141" t="s">
+        <v>4</v>
+      </c>
+      <c r="C141" t="s">
+        <v>7</v>
+      </c>
+      <c r="D141" s="1">
         <v>3.5249999999999999</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A142" s="1" t="s">
+      <c r="A142" t="s">
         <v>24</v>
       </c>
-      <c r="B142" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C142" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D142" s="2">
+      <c r="B142" t="s">
+        <v>4</v>
+      </c>
+      <c r="C142" t="s">
+        <v>7</v>
+      </c>
+      <c r="D142" s="1">
         <v>3.1150000000000002</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A143" s="1" t="s">
+      <c r="A143" t="s">
         <v>25</v>
       </c>
-      <c r="B143" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C143" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D143" s="2">
+      <c r="B143" t="s">
+        <v>4</v>
+      </c>
+      <c r="C143" t="s">
+        <v>7</v>
+      </c>
+      <c r="D143" s="1">
         <v>0.55800000000000005</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A144" s="1" t="s">
+      <c r="A144" t="s">
         <v>26</v>
       </c>
-      <c r="B144" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C144" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D144" s="2">
+      <c r="B144" t="s">
+        <v>4</v>
+      </c>
+      <c r="C144" t="s">
+        <v>7</v>
+      </c>
+      <c r="D144" s="1">
         <v>2.5550000000000002</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A145" s="1" t="s">
+      <c r="A145" t="s">
         <v>27</v>
       </c>
-      <c r="B145" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C145" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D145" s="2">
+      <c r="B145" t="s">
+        <v>4</v>
+      </c>
+      <c r="C145" t="s">
+        <v>7</v>
+      </c>
+      <c r="D145" s="1">
         <v>1.1339999999999999</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A146" s="1" t="s">
+      <c r="A146" t="s">
         <v>28</v>
       </c>
-      <c r="B146" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C146" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D146" s="2">
+      <c r="B146" t="s">
+        <v>4</v>
+      </c>
+      <c r="C146" t="s">
+        <v>7</v>
+      </c>
+      <c r="D146" s="1">
         <v>0.96799999999999997</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A147" s="1" t="s">
+      <c r="A147" t="s">
         <v>29</v>
       </c>
-      <c r="B147" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C147" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D147" s="2">
+      <c r="B147" t="s">
+        <v>4</v>
+      </c>
+      <c r="C147" t="s">
+        <v>7</v>
+      </c>
+      <c r="D147" s="1">
         <v>1.3240000000000001</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A148" s="1" t="s">
+      <c r="A148" t="s">
         <v>30</v>
       </c>
-      <c r="B148" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C148" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D148" s="2">
+      <c r="B148" t="s">
+        <v>4</v>
+      </c>
+      <c r="C148" t="s">
+        <v>7</v>
+      </c>
+      <c r="D148" s="1">
         <v>0.71099999999999997</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A149" s="1" t="s">
+      <c r="A149" t="s">
         <v>31</v>
       </c>
-      <c r="B149" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C149" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D149" s="2">
+      <c r="B149" t="s">
+        <v>4</v>
+      </c>
+      <c r="C149" t="s">
+        <v>7</v>
+      </c>
+      <c r="D149" s="1">
         <v>0.11</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A150" s="1" t="s">
+      <c r="A150" t="s">
         <v>32</v>
       </c>
-      <c r="B150" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C150" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D150" s="2">
+      <c r="B150" t="s">
+        <v>4</v>
+      </c>
+      <c r="C150" t="s">
+        <v>7</v>
+      </c>
+      <c r="D150" s="1">
         <v>2.379</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A151" s="1" t="s">
+      <c r="A151" t="s">
         <v>33</v>
       </c>
-      <c r="B151" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C151" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D151" s="2">
+      <c r="B151" t="s">
+        <v>4</v>
+      </c>
+      <c r="C151" t="s">
+        <v>7</v>
+      </c>
+      <c r="D151" s="1">
         <v>1.5309999999999999</v>
       </c>
     </row>
@@ -2646,8 +2642,5 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
-  <headerFooter>
-    <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Arial"&amp;10&amp;K000000 ---Internal Use--- </oddFooter>
-  </headerFooter>
 </worksheet>
 </file>